--- a/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>09.08.2024 16:15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cosso F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>16 917</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7 139</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Monza</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>514</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>CEv2hvmq</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>nesta alessandro</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>09.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Di Marco D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Genoa</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>dnnqk0iD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>09.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Scatena G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5 850</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Udinese</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Avellino</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>WE57Jh0D</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>pazienza michele</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>09.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prontera A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2 000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Sassuolo</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>gorini edoardo</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>773</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1449 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BJ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_away</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>8x0Cb1B6</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>fonseca paulo</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>GrNwFMem</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>24.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Doveri D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>771</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>24.08.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Perenzoni D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stadio Marco Druso
+ (Bolzano)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5 539</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Scatena G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Braglia
+ (Modena)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21 092</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10 248</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="AY5" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ5"/>
+  <dimension ref="A1:BJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,250 +738,250 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.08.2024 13:30</t>
+          <t>25.08.2024 13:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sacchi J. L.
+          <t>Sozza S.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27 906</t>
+          <t>43 147</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AC Milan</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>394</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>394</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>311</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>lQEaJ9QD</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>pecchia fabio</t>
+          <t>palladino raffaele</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>fonseca paulo</t>
+          <t>di francesco eusebio</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -1010,32 +1010,36 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.08.2024 13:30</t>
+          <t>25.08.2024 13:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Doveri D.
+          <t>Rapuano A.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25 144</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>20 451</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1048,212 +1052,212 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>298</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>431</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>ncu4OLs5</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>runjaic kosta</t>
+          <t>vanoli paolo</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>baroni marco</t>
+          <t>gasperini gian piero</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -1270,16 +1274,8 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
@@ -1290,249 +1286,257 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CjGqFjre</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.08.2024 14:30</t>
+          <t>24.08.2024 15:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Perenzoni D.
+          <t>Di Marco D.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Marco Druso
- (Bolzano)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5 539</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>W02MZDnp</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Sudtirol</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Mq05g4BP</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Salernitana</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>645</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>317</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>valente federico</t>
+          <t>inzaghi simone</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>OjWmexQb</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>martusciello giovanni</t>
+          <t>gotti luca</t>
         </is>
       </c>
       <c r="AY4" t="n">
         <v>77</v>
       </c>
       <c r="AZ4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -1544,287 +1548,267 @@
       </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4CX22Dbk</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.08.2024 15:30</t>
+          <t>24.08.2024 15:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scatena G.
+          <t>Mariani M.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Alberto Braglia
- (Modena)</t>
+          <t>Brianteo
+ (Monza)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21 092</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10 248</t>
-        </is>
-      </c>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>MBn63swN</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Modena</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>xIkUr2vO</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Bari</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>59%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>623</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>256</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>561</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>bisoli pierpaolo</t>
+          <t>nesta alessandro</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>nZ24J27c</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>longo moreno</t>
+          <t>gilardino alberto</t>
         </is>
       </c>
       <c r="AY5" t="n">
         <v>77</v>
       </c>
       <c r="AZ5" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -1836,34 +1820,1734 @@
       </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr">
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Galipo S.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stadio Mario Rigamonti
+ (Brescia)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>gorini edoardo</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ghersini D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Giovanni Zini
+ (Cremona)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20 641</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>stroppa giovanni</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8 811</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cosso F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23 061</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>pirlo andrea</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Massimi L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5 017</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pezzuto I.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Picco
+ (La Spezia)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>11 466</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>vivarini vincenzo</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,286 +696,292 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>tackles_home</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>tackles_away</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>clearances_completed_home</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>clearances_completed_away</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_home</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_away</t>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.08.2024 15:45</t>
+          <t>30.08.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Giua A.
+          <t>Marchetti M.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39 211</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>29 575</t>
-        </is>
-      </c>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>561</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>443</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>OW6PtuKn</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>zanetti paolo</t>
+          <t>inzaghi simone</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>motta thiago</t>
+          <t>gasperini gian piero</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -998,258 +1004,256 @@
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26.08.2024 13:30</t>
+          <t>30.08.2024 13:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Di Bello M.
+          <t>Marcenaro M.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unipol Domus
- (Cagliari)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16 416</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>16 365</t>
-        </is>
-      </c>
+          <t>11 150</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>401</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>566</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>291</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>433</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>125</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>nicola davide</t>
+          <t>di francesco eusebio</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>fabregas cesc</t>
+          <t>vanoli paolo</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -1266,271 +1270,273 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>zVpmZBZQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25.08.2024 15:45</t>
+          <t>28.08.2024 15:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Zufferli L.
+          <t>Collu G.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Dino Manuzzi
+ (Cesena)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>23 860</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>67 517</t>
+          <t>11 870</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Empoli</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>xjigzK81</t>
+          <t>vD8aDRIm</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>de rossi daniele</t>
+          <t>mignani michele</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>d aversa roberto</t>
+          <t>caserta fabio</t>
         </is>
       </c>
       <c r="AY4" t="n">
         <v>77</v>
       </c>
       <c r="AZ4" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -1540,271 +1546,289 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>SSPRRTR0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.08.2024 15:45</t>
+          <t>28.08.2024 15:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pairetto L.
+          <t>Di Marco D.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Stadio San Vito-Luigi Marulla
+ (Cosenza)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>54 726</t>
+          <t>20 987</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45 000</t>
+          <t>8 006</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>39%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>61%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>305</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>152</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>23vSAc12</t>
+          <t>Yika9O16</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>conte antonio</t>
+          <t>alvini massimiliano</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>O6SinSSs</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>italiano vincenzo</t>
+          <t>d angelo luca</t>
         </is>
       </c>
       <c r="AY5" t="n">
         <v>77</v>
       </c>
       <c r="AZ5" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -1814,256 +1838,282 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCxNBHy3</t>
+          <t>p4dhrkCs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.08.2024 15:30</t>
+          <t>28.08.2024 15:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rutella D.
+          <t>Perri M.
  (Ita)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Nicola Ceravolo
- (Catanzaro)</t>
+          <t>Stadio Leonardo Garilli
+ (Piacenza)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14 650</t>
+          <t>21 668</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11 788</t>
+          <t>1 480</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GnizyMB7</t>
+          <t>hKSfjtsQ</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>hKSfjtsQ</t>
+          <t>z7WK5Pwb</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>519</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>449</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>nsYMfLJM</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>caserta fabio</t>
+          <t>pagliuca guido</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>tvh4IkLf</t>
+          <t>hrkecaMB</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>pagliuca guido</t>
+          <t>possanzini davide</t>
         </is>
       </c>
       <c r="AY6" t="n">
@@ -2082,278 +2132,280 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvdW7ZzS</t>
+          <t>Y54hDUC7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25.08.2024 15:30</t>
+          <t>27.08.2024 15:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Crezzini V.
+          <t>La Penna F.
  (Ita)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Danilo Martelli
- (Mantova)</t>
+          <t>Stadio San Nicola
+ (Bari)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5 423</t>
+          <t>58 270</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8 262</t>
+          <t>15 733</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>z7WK5Pwb</t>
+          <t>xIkUr2vO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>p84TeBhA</t>
+          <t>QDdvI0zl</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>444</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>353</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>292</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>hrkecaMB</t>
+          <t>nZ24J27c</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>possanzini davide</t>
+          <t>longo moreno</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Yika9O16</t>
+          <t>bPHSQi9q</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>alvini massimiliano</t>
+          <t>grosso fabio</t>
         </is>
       </c>
       <c r="AY7" t="n">
@@ -2372,32 +2424,1794 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Monaldi M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1 987</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Arena A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Pier Cesare Tombolato
+ (Cittadella)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7 623</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3 685</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>8dDPzPa7</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>gorini edoardo</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fourneau F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Giovanni Zini
+ (Cremona)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20 641</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9 394</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>YgLhKnOo</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>stroppa giovanni</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Piccinini M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Benito Stirpe
+ (Frosinone)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>16 227</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9 841</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>dnLs0wVo</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>vivarini vincenzo</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9 252</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>27</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Feliciani E.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>15 683</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>2kfSDavF</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>pirlo andrea</t>
+        </is>
+      </c>
+      <c r="AY13" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ9"/>
+  <dimension ref="A1:BJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,22 +696,22 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>crosses_completed_home</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>crosses_completed_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>red_cards_home</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>red_cards_away</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -738,250 +738,254 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31.08.2024 15:45</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Massa D.
+          <t>Guida M.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70 634</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>41 375</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AC Milan</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>119</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>S8Ygn9ME</t>
+          <t>bBhpZV2s</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>baroni marco</t>
+          <t>motta thiago</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>fonseca paulo</t>
+          <t>de rossi daniele</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -1010,34 +1014,34 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marinelli L.
+          <t>Prontera A.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>38 279</t>
+          <t>25 144</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25 960</t>
+          <t>7 020</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1047,217 +1051,217 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Empoli</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>32%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>427</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>535</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>446</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>italiano vincenzo</t>
+          <t>runjaic kosta</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>YXIDwoe5</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>d aversa roberto</t>
+          <t>fabregas cesc</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -1274,16 +1278,8 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
@@ -1294,254 +1290,254 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
+          <t>01.09.2024 13:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fabbri M.
+          <t>Colombo A.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40 670</t>
+          <t>43 147</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26 386</t>
+          <t>18 376</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>570</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>490</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>KtGrCa5d</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>gotti luca</t>
+          <t>palladino raffaele</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>MLVBCoYg</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>nicola davide</t>
+          <t>nesta alessandro</t>
         </is>
       </c>
       <c r="AY4" t="n">
@@ -1558,26 +1554,10 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
@@ -1586,32 +1566,36 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dtLQNtsB</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.08.2024 15:30</t>
+          <t>01.09.2024 13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cosso F.
+          <t>Ayroldi G.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Alberto Braglia
- (Modena)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21 092</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30 747</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1619,216 +1603,224 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>MBn63swN</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Modena</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>C0yUqo8c</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Cittadella</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>58%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>454</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>327</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>bisoli pierpaolo</t>
+          <t>gilardino alberto</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>gorini edoardo</t>
+          <t>zanetti paolo</t>
         </is>
       </c>
       <c r="AY5" t="n">
         <v>77</v>
       </c>
       <c r="AZ5" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -1838,68 +1830,48 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Ofy73Ced</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31.08.2024 15:30</t>
+          <t>31.08.2024 15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Galipo S.
+          <t>Tremolada P.
  (Ita)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Arena Garibaldi - Stadio Romeo Anconetani
- (Pisa)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14 869</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2</t>
@@ -1912,211 +1884,219 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>roasMsOT</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6ulJbMCe</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Reggiana</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>459</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>395</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>GfucctAF</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>inzaghi filippo</t>
+          <t>conte antonio</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gfur2NmR</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>viali william</t>
+          <t>pecchia fabio</t>
         </is>
       </c>
       <c r="AY6" t="n">
         <v>77</v>
       </c>
       <c r="AZ6" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -2128,276 +2108,272 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CGH1PgIF</t>
+          <t>v5l07LdU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.08.2024 15:30</t>
+          <t>01.09.2024 15:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Manganiello G.
+          <t>Perenzoni D.
  (Ita)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mapei Stadium – Città del Tricolore
- (Reggio Emilia)</t>
+          <t>Stadio Nicola Ceravolo
+ (Catanzaro)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21 525</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>14 650</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9 348</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>QDdvI0zl</t>
+          <t>GnizyMB7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>KUzfp5N3</t>
+          <t>hG4fg4z3</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>444</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>505</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>bPHSQi9q</t>
+          <t>nsYMfLJM</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>grosso fabio</t>
+          <t>caserta fabio</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>lSb6U6l0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>stroppa giovanni</t>
+          <t>calabro antonio</t>
         </is>
       </c>
       <c r="AY7" t="n">
@@ -2414,210 +2390,206 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>21OYHBAk</t>
+          <t>fHO9ROsn</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31.08.2024 15:30</t>
+          <t>01.09.2024 15:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rutella D.
+          <t>Bonacina K.
  (Ita)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Marco Druso
- (Bolzano)</t>
+          <t>Stadio Benito Stirpe
+ (Frosinone)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5 539</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>16 227</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10 755</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>W02MZDnp</t>
+          <t>pfo9H1Wp</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>jci0qO9B</t>
+          <t>hKSfjtsQ</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
           <t>3</t>
@@ -2625,67 +2597,67 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>435</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>339</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>bmzifXwb</t>
+          <t>dnLs0wVo</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>valente federico</t>
+          <t>vivarini vincenzo</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lb1XFX3n</t>
+          <t>tvh4IkLf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>maran rolando</t>
+          <t>pagliuca guido</t>
         </is>
       </c>
       <c r="AY8" t="n">
@@ -2704,276 +2676,280 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>v3JgRFm3</t>
+          <t>jqIIP2Cb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31.08.2024 13:00</t>
+          <t>01.09.2024 15:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Maresca F.
+          <t>Abisso R.
  (Ita)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Danilo Martelli
+ (Mantova)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36 599</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>5 423</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8 651</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nJbCGx2U</t>
+          <t>z7WK5Pwb</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>xIkUr2vO</t>
+          <t>Mq05g4BP</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>513</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>413</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>447</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>AZ1NG9tC</t>
+          <t>hrkecaMB</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>sottil andrea</t>
+          <t>possanzini davide</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>nZ24J27c</t>
+          <t>OjWmexQb</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>longo moreno</t>
+          <t>martusciello giovanni</t>
         </is>
       </c>
       <c r="AY9" t="n">
@@ -2990,44 +2966,596 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>GUXb5YQq</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Massimi L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Renzo Barbera
+ (Palermo)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>36 349</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>25 787</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WIX2NXnS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Aureliano G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Picco
+ (La Spezia)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>11 466</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>7 573</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Cesena</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>vD8aDRIm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>mignani michele</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,187 +728,191 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>v1I9TP43</t>
+          <t>rgFQPs4S</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.09.2024 13:00</t>
+          <t>16.09.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Di Bello M.
+          <t>Zufferli L.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Carlo Castellani
- (Empoli)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16 284</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Empoli</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AL2" t="inlineStr">
         <is>
           <t>2</t>
@@ -916,62 +920,62 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>502</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>419</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>MBrKQFV7</t>
+          <t>S8Ygn9ME</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>d aversa roberto</t>
+          <t>baroni marco</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>bBhpZV2s</t>
+          <t>OW6PtuKn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>motta thiago</t>
+          <t>zanetti paolo</t>
         </is>
       </c>
       <c r="AY2" t="n">
@@ -998,32 +1002,36 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>n7VN5MCd</t>
+          <t>WIJkQBF8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14.09.2024 10:00</t>
+          <t>16.09.2024 13:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Piccinini M.
+          <t>Abisso R.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Sinigaglia
- (Como)</t>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13 602</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>17 586</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1031,217 +1039,217 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>56%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>496</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>428</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>YXIDwoe5</t>
+          <t>lQEaJ9QD</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>fabregas cesc</t>
+          <t>pecchia fabio</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>tjY4uUem</t>
+          <t>ncu4OLs5</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>italiano vincenzo</t>
+          <t>runjaic kosta</t>
         </is>
       </c>
       <c r="AY3" t="n">
@@ -1258,8 +1266,16 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
@@ -1268,181 +1284,189 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OGCsGku2</t>
+          <t>Esk5Iad2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14.09.2024 10:00</t>
+          <t>15.09.2024 15:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pezzuto I.
+          <t>Pairetto L.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio San Nicola
- (Bari)</t>
+          <t>Brianteo
+ (Monza)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58 270</t>
+          <t>17 102</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14 003</t>
+          <t>14 541</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>xIkUr2vO</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Bari</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>z7WK5Pwb</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Mantova</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1452,69 +1476,69 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>637</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>338</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>146</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>nZ24J27c</t>
+          <t>CEv2hvmq</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>longo moreno</t>
+          <t>nesta alessandro</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>hrkecaMB</t>
+          <t>j32a3mqs</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>possanzini davide</t>
+          <t>inzaghi simone</t>
         </is>
       </c>
       <c r="AY4" t="n">
         <v>77</v>
       </c>
       <c r="AZ4" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -1524,287 +1548,271 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jN4TwgX8</t>
+          <t>6cNF7rrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.09.2024 10:00</t>
+          <t>15.09.2024 13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ghersini D.
+          <t>La Penna F.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Mario Rigamonti
- (Brescia)</t>
+          <t>Unipol Domus
+ (Cagliari)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19 500</t>
+          <t>16 416</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5 715</t>
+          <t>15 733</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>jci0qO9B</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>pfo9H1Wp</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>335</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>lb1XFX3n</t>
+          <t>MLVBCoYg</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>maran rolando</t>
+          <t>nicola davide</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>dnLs0wVo</t>
+          <t>23vSAc12</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>vivarini vincenzo</t>
+          <t>conte antonio</t>
         </is>
       </c>
       <c r="AY5" t="n">
         <v>77</v>
       </c>
       <c r="AZ5" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -1814,110 +1822,94 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OUiGUlfe</t>
+          <t>zFWqD4KM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14.09.2024 10:00</t>
+          <t>15.09.2024 10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Feliciani E.
+          <t>Sacchi J. L.
  (Ita)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Pier Cesare Tombolato
- (Cittadella)</t>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7 623</t>
+          <t>24 950</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2 269</t>
+          <t>22 705</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C0yUqo8c</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>GnizyMB7</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1927,174 +1919,174 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>395</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>336</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>308</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>8dDPzPa7</t>
+          <t>EJLKYOzb</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>gorini edoardo</t>
+          <t>gasperini gian piero</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>nsYMfLJM</t>
+          <t>619UPLrb</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>caserta fabio</t>
+          <t>palladino raffaele</t>
         </is>
       </c>
       <c r="AY6" t="n">
         <v>77</v>
       </c>
       <c r="AZ6" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -2106,273 +2098,269 @@
       </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CjYAjWGE</t>
+          <t>4WHcOkpL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14.09.2024 10:00</t>
+          <t>15.09.2024 10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Perenzoni D.
+          <t>Colombo A.
  (Ita)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Giovanni Zini
- (Cremona)</t>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20 641</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>24 277</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>KUzfp5N3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Cremonese</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>re6VD39b</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Spezia</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>452</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>323</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>YgLhKnOo</t>
+          <t>AB3WB3pA</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>stroppa giovanni</t>
+          <t>vanoli paolo</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>O6SinSSs</t>
+          <t>KtGrCa5d</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>d angelo luca</t>
+          <t>gotti luca</t>
         </is>
       </c>
       <c r="AY7" t="n">
         <v>77</v>
       </c>
       <c r="AZ7" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="BA7" t="n">
         <v>0</v>
@@ -2384,56 +2372,44 @@
       </c>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>b7WIlAoR</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14.09.2024 10:00</t>
+          <t>15.09.2024 07:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sozza S.
+          <t>Giua A.
  (Ita)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Romeo Menti
- (Castellammare di Stabia)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13 000</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>33 009</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>1</t>
@@ -2441,216 +2417,224 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>hKSfjtsQ</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Juve Stabia</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>n38Nktmn</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>381</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>420</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>324</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>349</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>tvh4IkLf</t>
+          <t>tSiEeKvS</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>pagliuca guido</t>
+          <t>gilardino alberto</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Wn0poKgt</t>
+          <t>xjigzK81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>dionisi alessio</t>
+          <t>de rossi daniele</t>
         </is>
       </c>
       <c r="AY8" t="n">
         <v>77</v>
       </c>
       <c r="AZ8" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -2662,277 +2646,269 @@
       </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>S2b7WAPr</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13.09.2024 15:30</t>
+          <t>14.09.2024 15:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Monaldi M.
+          <t>Di Marco D.
  (Ita)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Dino Manuzzi
- (Cesena)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23 860</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13 974</t>
+          <t>71 273</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>xddf1qfh</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Cesena</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>MBn63swN</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Modena</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>59%</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>571</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>338</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>525</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>284</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>vD8aDRIm</t>
+          <t>KAwSWnoE</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>mignani michele</t>
+          <t>fonseca paulo</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>YTZ7S7pk</t>
+          <t>n10g3KfJ</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>bisoli pierpaolo</t>
+          <t>di francesco eusebio</t>
         </is>
       </c>
       <c r="AY9" t="n">
         <v>77</v>
       </c>
       <c r="AZ9" t="n">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -2952,24 +2928,1136 @@
           <t>1</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>j5BcsSw1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bonacina K.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>15 083</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WWCyxX1L</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mariani M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Arena Garibaldi - Stadio Romeo Anconetani
+ (Pisa)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>14 869</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2 777</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Carrarese</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>lSb6U6l0</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>calabro antonio</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WfeOSSO7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Collu G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stadio San Vito-Luigi Marulla
+ (Cosenza)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20 987</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8 171</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Sampdoria</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>AZ1NG9tC</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>sottil andrea</t>
+        </is>
+      </c>
+      <c r="AY12" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>23</t>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IiDkql9l</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Crezzini V.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mapei Stadium – Città del Tricolore
+ (Reggio Emilia)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>21 525</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8 665</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>Gfur2NmR</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>viali william</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="AY13" t="n">
+        <v>77</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>774</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
     </row>

--- a/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,2641 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>SznSCTAl</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>19.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chiffi D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>fonseca paulo</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>ncu4OLs5</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>runjaic kosta</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>771</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>13 602</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>fabregas cesc</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>771</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Doveri D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>tjY4uUem</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>italiano vincenzo</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>771</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4MfFXWSP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19.10.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prontera A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadio Mario Rigamonti
+ (Brescia)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Brescia</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lb1XFX3n</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>maran rolando</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>bPHSQi9q</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>grosso fabio</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>774</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Imw2OSkC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Pezzuto I.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stadio Pier Cesare Tombolato
+ (Cittadella)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7 623</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Cosenza</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>8xV5hB5e</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>dal canto alessandro</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Yika9O16</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>alvini massimiliano</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>774</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>UR6KtA5t</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Rapuano A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Alberto Braglia
+ (Modena)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>21 092</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Modena</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>YTZ7S7pk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>bisoli pierpaolo</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Wn0poKgt</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>dionisi alessio</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>774</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dvbywS45</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ghersini D.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stadio Arechi
+ (Salerno)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>37 800</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Salernitana</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>OjWmexQb</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>martusciello giovanni</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>O6SinSSs</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>d angelo luca</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>774</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>441qy6ZH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Marchetti M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Marco Druso
+ (Bolzano)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5 539</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sudtirol</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>bmzifXwb</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>valente federico</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>GfucctAF</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>inzaghi filippo</t>
+        </is>
+      </c>
+      <c r="BA9" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>774</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xG2T9TzJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio San Nicola
+ (Bari)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>58 270</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>18 615</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Catanzaro</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>nZ24J27c</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>longo moreno</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>nsYMfLJM</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>caserta fabio</t>
+        </is>
+      </c>
+      <c r="BA10" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>774</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/italy/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>04.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ayroldi G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>35 000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>S8Ygn9ME</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>baroni marco</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>MLVBCoYg</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>nicola davide</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>771</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>04.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Di Bello M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8 102</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>MBrKQFV7</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>d aversa roberto</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>YXIDwoe5</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>fabregas cesc</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>771</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>04.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Guida M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>16 151</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lQEaJ9QD</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>pecchia fabio</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>tSiEeKvS</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>gilardino alberto</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>77</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>771</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>